--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$182</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8489" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7215" uniqueCount="747">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Verlaufsmeldung mit Meldedatum (M01), Melder (M02), Nachsorge-Art (M03), Vitalstatus (M04), Tumorstatus lokal/LK/FM (M05-M07, geerbt von MII Verlauf), und Zweittumor (M08-M10). Erweitert MII_PR_Onko_Verlauf um OncoBox-2.0-spezifische Felder. Wird sowohl fuer Gesamtbeurteilung nach definitiver Therapie (D27) als auch fuer Nachsorge-Follow-Up (M06) verwendet — Unterscheidung ueber effectiveDateTime.</t>
+    <t>Verlaufsmeldung mit Meldedatum (M01), Melder (M02), Nachsorge-Art als method (M03), Tumorstatus lokal/LK/FM (M05-M07, geerbt von MII Verlauf), und Zweittumor-Flag (M08). Vitalstatus (M04) wird ueber Patient.deceased abgebildet. Zweittumor-Details (M09-M10) werden als eigene Condition dokumentiert.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1470,22 +1470,19 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>How it was done</t>
+    <t>Art der Nachsorge (M03)</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>
   </si>
   <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
+    <t>Aktive Nachsorge = Patientin persoenlich untersucht. Passive Nachsorge = Information aus Akten/Registern.</t>
   </si>
   <si>
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>https://www.senologie.org/fhir/ValueSet/vs-senologie-nachsorge-art</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2294,100 +2291,6 @@
     <t>Observation.component:Fernmetastasen_Verlauf.referenceRange</t>
   </si>
   <si>
-    <t>Observation.component:nachsorgeArt</t>
-  </si>
-  <si>
-    <t>nachsorgeArt</t>
-  </si>
-  <si>
-    <t>Art der Nachsorge (M03)</t>
-  </si>
-  <si>
-    <t>Aktive Nachsorge = Patientin persönlich untersucht. Passive Nachsorge = Information aus Akten/Registern.</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.id</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
-    &lt;code value="nachsorge-art"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.value[x]</t>
-  </si>
-  <si>
-    <t>https://www.senologie.org/fhir/ValueSet/vs-senologie-nachsorge-art</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:nachsorgeArt.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus</t>
-  </si>
-  <si>
-    <t>vitalstatus</t>
-  </si>
-  <si>
-    <t>Vitalstatus der Patientin (M04)</t>
-  </si>
-  <si>
-    <t>Vitalstatus zum Meldezeitpunkt: lebend, verstorben oder unbekannt.</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.id</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
-    &lt;code value="vitalstatus"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.value[x]</t>
-  </si>
-  <si>
-    <t>https://www.senologie.org/fhir/ValueSet/vs-senologie-vitalstatus</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:vitalstatus.referenceRange</t>
-  </si>
-  <si>
     <t>Observation.component:zweittumor</t>
   </si>
   <si>
@@ -2397,7 +2300,7 @@
     <t>Zweittumor diagnostiziert (M08)</t>
   </si>
   <si>
-    <t>Wurde bei der Patientin ein zweiter Primärtumor (nicht Rezidiv/Metastase) diagnostiziert?</t>
+    <t>Wurde bei der Patientin ein zweiter Primaertumor (nicht Rezidiv/Metastase) diagnostiziert? Details (ICD, Datum) werden als eigene Condition dokumentiert.</t>
   </si>
   <si>
     <t>Observation.component:zweittumor.id</t>
@@ -2412,12 +2315,22 @@
     <t>Observation.component:zweittumor.code</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
-    &lt;code value="zweittumor"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
+    <t>Observation.component:zweittumor.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:zweittumor.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:zweittumor.code.coding</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
+  &lt;code value="zweittumor"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:zweittumor.code.text</t>
   </si>
   <si>
     <t>Observation.component:zweittumor.value[x]</t>
@@ -2433,94 +2346,6 @@
   </si>
   <si>
     <t>Observation.component:zweittumor.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd</t>
-  </si>
-  <si>
-    <t>zweittumorIcd</t>
-  </si>
-  <si>
-    <t>ICD-10-GM Diagnose des Zweittumors (M09)</t>
-  </si>
-  <si>
-    <t>ICD-10-GM-Code der Zweittumor-Diagnose, nur wenn Zweittumor = ja.</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.id</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
-    &lt;code value="zweittumor-icd"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorIcd.referenceRange</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum</t>
-  </si>
-  <si>
-    <t>zweittumorDatum</t>
-  </si>
-  <si>
-    <t>Diagnosedatum des Zweittumors (M10)</t>
-  </si>
-  <si>
-    <t>Datum der Erstdiagnose des Zweittumors, nur wenn Zweittumor = ja.</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.id</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.extension</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="https://www.senologie.org/fhir/CodeSystem/cs-senologie-follow-up"/&gt;
-    &lt;code value="zweittumor-datum"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component:zweittumorDatum.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2837,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ214"/>
+  <dimension ref="A1:AQ182"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.02734375" customWidth="true" bestFit="true"/>
@@ -9322,7 +9147,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>466</v>
       </c>
@@ -9341,7 +9166,7 @@
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
@@ -9387,13 +9212,11 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y53" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -9435,10 +9258,10 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -9449,10 +9272,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9475,16 +9298,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9534,7 +9357,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9555,27 +9378,27 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9598,16 +9421,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9657,7 +9480,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9678,27 +9501,27 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AO55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9721,19 +9544,19 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9782,7 +9605,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9794,22 +9617,22 @@
         <v>105</v>
       </c>
       <c r="AJ56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AK56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -9820,10 +9643,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9941,10 +9764,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10064,14 +9887,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -10093,10 +9916,10 @@
         <v>116</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>119</v>
@@ -10151,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -10189,10 +10012,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10215,16 +10038,16 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10274,7 +10097,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -10283,25 +10106,25 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AJ60" t="s" s="2">
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AK60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>20</v>
@@ -10312,10 +10135,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10338,16 +10161,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10397,7 +10220,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10406,25 +10229,25 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AO61" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>20</v>
@@ -10435,10 +10258,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10464,16 +10287,16 @@
         <v>247</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -10501,11 +10324,11 @@
         <v>177</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
       </c>
@@ -10522,7 +10345,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10543,10 +10366,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>446</v>
@@ -10560,10 +10383,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10589,16 +10412,16 @@
         <v>247</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -10626,11 +10449,11 @@
         <v>163</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
       </c>
@@ -10647,7 +10470,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10668,10 +10491,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>446</v>
@@ -10685,10 +10508,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10711,19 +10534,19 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10772,7 +10595,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10784,22 +10607,22 @@
         <v>105</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>20</v>
@@ -10810,10 +10633,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10839,10 +10662,10 @@
         <v>109</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>401</v>
@@ -10895,7 +10718,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10919,10 +10742,10 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>20</v>
@@ -10933,10 +10756,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10959,16 +10782,16 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -11018,7 +10841,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11042,10 +10865,10 @@
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>20</v>
@@ -11056,10 +10879,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11082,16 +10905,16 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11141,7 +10964,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11165,10 +10988,10 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>20</v>
@@ -11179,10 +11002,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11205,19 +11028,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -11254,10 +11077,10 @@
         <v>20</v>
       </c>
       <c r="AB68" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AC68" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>20</v>
@@ -11266,7 +11089,7 @@
         <v>122</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11290,10 +11113,10 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>20</v>
@@ -11304,10 +11127,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11425,10 +11248,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11548,14 +11371,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11577,10 +11400,10 @@
         <v>116</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>119</v>
@@ -11635,7 +11458,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11673,10 +11496,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11702,13 +11525,13 @@
         <v>247</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>262</v>
@@ -11760,7 +11583,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>93</v>
@@ -11781,7 +11604,7 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>267</v>
@@ -11798,10 +11621,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11824,16 +11647,16 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>355</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>357</v>
@@ -11885,7 +11708,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11906,7 +11729,7 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>360</v>
@@ -11923,10 +11746,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11952,13 +11775,13 @@
         <v>247</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>431</v>
@@ -12010,7 +11833,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -12048,10 +11871,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12135,7 +11958,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -12173,10 +11996,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12202,16 +12025,16 @@
         <v>83</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="N76" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -12260,7 +12083,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12284,10 +12107,10 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>20</v>
@@ -12298,13 +12121,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>20</v>
@@ -12326,19 +12149,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M77" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -12387,7 +12210,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12411,10 +12234,10 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO77" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>20</v>
@@ -12425,10 +12248,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12546,10 +12369,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12669,14 +12492,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12698,10 +12521,10 @@
         <v>116</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>119</v>
@@ -12756,7 +12579,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12794,10 +12617,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12823,13 +12646,13 @@
         <v>247</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O81" t="s" s="2">
         <v>262</v>
@@ -12881,7 +12704,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>93</v>
@@ -12902,7 +12725,7 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>267</v>
@@ -12919,10 +12742,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13040,10 +12863,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13163,10 +12986,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13211,7 +13034,7 @@
         <v>20</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>20</v>
@@ -13288,10 +13111,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13409,10 +13232,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="B86" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13532,10 +13355,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B87" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13657,10 +13480,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13780,10 +13603,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B89" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13882,7 +13705,7 @@
         <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>20</v>
@@ -13905,10 +13728,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B90" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14030,10 +13853,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B91" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14155,10 +13978,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14280,10 +14103,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14309,13 +14132,13 @@
         <v>247</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>355</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>357</v>
@@ -14347,7 +14170,7 @@
       </c>
       <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -14365,7 +14188,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -14386,7 +14209,7 @@
         <v>20</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>360</v>
@@ -14403,10 +14226,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B94" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14524,10 +14347,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B95" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14647,10 +14470,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14676,10 +14499,10 @@
         <v>149</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>276</v>
@@ -14772,10 +14595,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14893,10 +14716,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15016,10 +14839,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15141,10 +14964,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15264,10 +15087,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15389,10 +15212,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15514,10 +15337,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15639,10 +15462,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15764,10 +15587,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15793,13 +15616,13 @@
         <v>247</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O105" t="s" s="2">
         <v>431</v>
@@ -15851,7 +15674,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15889,10 +15712,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15976,7 +15799,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16014,10 +15837,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16043,16 +15866,16 @@
         <v>83</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M107" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="N107" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -16101,7 +15924,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -16125,10 +15948,10 @@
         <v>20</v>
       </c>
       <c r="AN107" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>20</v>
@@ -16139,13 +15962,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>20</v>
@@ -16167,19 +15990,19 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M108" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>20</v>
@@ -16228,7 +16051,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -16252,10 +16075,10 @@
         <v>20</v>
       </c>
       <c r="AN108" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>20</v>
@@ -16266,10 +16089,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16387,10 +16210,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16510,14 +16333,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -16539,10 +16362,10 @@
         <v>116</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>119</v>
@@ -16597,7 +16420,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16635,10 +16458,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16664,13 +16487,13 @@
         <v>247</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O112" t="s" s="2">
         <v>262</v>
@@ -16722,7 +16545,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>93</v>
@@ -16743,7 +16566,7 @@
         <v>20</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>267</v>
@@ -16760,10 +16583,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16881,10 +16704,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17004,10 +16827,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17052,7 +16875,7 @@
         <v>20</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>20</v>
@@ -17129,10 +16952,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17250,10 +17073,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17373,10 +17196,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17498,10 +17321,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17621,10 +17444,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17723,7 +17546,7 @@
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>20</v>
@@ -17746,10 +17569,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17871,10 +17694,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17996,10 +17819,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18121,10 +17944,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18150,13 +17973,13 @@
         <v>247</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M124" t="s" s="2">
         <v>355</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>357</v>
@@ -18188,7 +18011,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -18206,7 +18029,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
@@ -18227,7 +18050,7 @@
         <v>20</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>360</v>
@@ -18244,10 +18067,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18365,10 +18188,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18488,10 +18311,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18517,10 +18340,10 @@
         <v>149</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>679</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>276</v>
@@ -18613,10 +18436,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18734,10 +18557,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18857,10 +18680,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18982,10 +18805,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19105,10 +18928,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19230,10 +19053,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19355,10 +19178,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19480,10 +19303,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19605,10 +19428,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19634,13 +19457,13 @@
         <v>247</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O136" t="s" s="2">
         <v>431</v>
@@ -19692,7 +19515,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19730,10 +19553,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19817,7 +19640,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19855,10 +19678,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19884,16 +19707,16 @@
         <v>83</v>
       </c>
       <c r="L138" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M138" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="N138" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O138" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -19942,7 +19765,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19966,10 +19789,10 @@
         <v>20</v>
       </c>
       <c r="AN138" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AO138" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP138" t="s" s="2">
         <v>20</v>
@@ -19980,13 +19803,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>20</v>
@@ -20008,19 +19831,19 @@
         <v>94</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="M139" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N139" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="N139" t="s" s="2">
+      <c r="O139" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -20069,7 +19892,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -20093,10 +19916,10 @@
         <v>20</v>
       </c>
       <c r="AN139" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AP139" t="s" s="2">
         <v>20</v>
@@ -20107,10 +19930,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20228,10 +20051,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20351,14 +20174,14 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -20380,10 +20203,10 @@
         <v>116</v>
       </c>
       <c r="L142" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M142" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>119</v>
@@ -20438,7 +20261,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -20476,10 +20299,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20505,13 +20328,13 @@
         <v>247</v>
       </c>
       <c r="L143" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M143" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M143" t="s" s="2">
+      <c r="N143" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O143" t="s" s="2">
         <v>262</v>
@@ -20563,7 +20386,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>93</v>
@@ -20584,7 +20407,7 @@
         <v>20</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>267</v>
@@ -20601,10 +20424,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20722,10 +20545,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20845,10 +20668,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20893,7 +20716,7 @@
         <v>20</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>20</v>
@@ -20970,10 +20793,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21091,10 +20914,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21214,10 +21037,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21339,10 +21162,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21462,10 +21285,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21564,7 +21387,7 @@
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>20</v>
@@ -21587,10 +21410,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21712,10 +21535,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21837,10 +21660,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21962,10 +21785,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21991,13 +21814,13 @@
         <v>247</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M155" t="s" s="2">
         <v>355</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>357</v>
@@ -22029,7 +21852,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>20</v>
@@ -22047,7 +21870,7 @@
         <v>20</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22068,7 +21891,7 @@
         <v>20</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>360</v>
@@ -22085,10 +21908,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22206,10 +22029,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22329,10 +22152,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22358,10 +22181,10 @@
         <v>149</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>276</v>
@@ -22454,10 +22277,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22575,10 +22398,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22698,10 +22521,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22823,10 +22646,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22946,10 +22769,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23071,10 +22894,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23196,10 +23019,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23321,10 +23144,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23446,10 +23269,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23475,13 +23298,13 @@
         <v>247</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="O167" t="s" s="2">
         <v>431</v>
@@ -23533,7 +23356,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23571,10 +23394,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23658,7 +23481,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23696,10 +23519,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23725,16 +23548,16 @@
         <v>83</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M169" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="M169" t="s" s="2">
-        <v>593</v>
-      </c>
       <c r="N169" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O169" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>20</v>
@@ -23783,7 +23606,7 @@
         <v>20</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23807,10 +23630,10 @@
         <v>20</v>
       </c>
       <c r="AN169" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AO169" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO169" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AP169" t="s" s="2">
         <v>20</v>
@@ -23821,13 +23644,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C170" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>20</v>
@@ -23849,19 +23672,19 @@
         <v>94</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="N170" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="M170" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>733</v>
-      </c>
       <c r="O170" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>20</v>
@@ -23910,7 +23733,7 @@
         <v>20</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23934,10 +23757,10 @@
         <v>20</v>
       </c>
       <c r="AN170" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO170" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AO170" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AP170" t="s" s="2">
         <v>20</v>
@@ -23948,10 +23771,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24069,10 +23892,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24192,14 +24015,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -24221,10 +24044,10 @@
         <v>116</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>119</v>
@@ -24279,7 +24102,7 @@
         <v>20</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24317,10 +24140,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24346,13 +24169,13 @@
         <v>247</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M174" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="O174" t="s" s="2">
         <v>262</v>
@@ -24365,7 +24188,7 @@
         <v>20</v>
       </c>
       <c r="S174" t="s" s="2">
-        <v>738</v>
+        <v>20</v>
       </c>
       <c r="T174" t="s" s="2">
         <v>20</v>
@@ -24404,7 +24227,7 @@
         <v>20</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>93</v>
@@ -24425,7 +24248,7 @@
         <v>20</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>267</v>
@@ -24442,10 +24265,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24465,23 +24288,19 @@
         <v>20</v>
       </c>
       <c r="J175" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>247</v>
+        <v>109</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>583</v>
+        <v>110</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>20</v>
       </c>
@@ -24505,11 +24324,13 @@
         <v>20</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y175" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z175" t="s" s="2">
-        <v>740</v>
+        <v>20</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>20</v>
@@ -24527,7 +24348,7 @@
         <v>20</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>581</v>
+        <v>112</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24536,10 +24357,10 @@
         <v>93</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>20</v>
@@ -24548,38 +24369,38 @@
         <v>20</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>585</v>
+        <v>20</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>361</v>
+        <v>113</v>
       </c>
       <c r="AP175" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>20</v>
@@ -24591,20 +24412,18 @@
         <v>20</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>247</v>
+        <v>116</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>587</v>
+        <v>117</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>588</v>
+        <v>118</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>20</v>
       </c>
@@ -24628,43 +24447,43 @@
         <v>20</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>586</v>
+        <v>123</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>20</v>
@@ -24676,10 +24495,10 @@
         <v>20</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>435</v>
+        <v>113</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>20</v>
@@ -24690,18 +24509,18 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>437</v>
+        <v>20</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G177" t="s" s="2">
         <v>82</v>
@@ -24713,22 +24532,22 @@
         <v>20</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>438</v>
+        <v>274</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>439</v>
+        <v>275</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>440</v>
+        <v>276</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>441</v>
+        <v>277</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>20</v>
@@ -24738,7 +24557,7 @@
         <v>20</v>
       </c>
       <c r="S177" t="s" s="2">
-        <v>20</v>
+        <v>740</v>
       </c>
       <c r="T177" t="s" s="2">
         <v>20</v>
@@ -24753,13 +24572,13 @@
         <v>20</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>20</v>
@@ -24777,7 +24596,7 @@
         <v>20</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>590</v>
+        <v>279</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -24786,7 +24605,7 @@
         <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>106</v>
@@ -24798,27 +24617,27 @@
         <v>20</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>444</v>
+        <v>20</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>445</v>
+        <v>280</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>446</v>
+        <v>281</v>
       </c>
       <c r="AP177" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ177" t="s" s="2">
-        <v>447</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>591</v>
+        <v>623</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24829,7 +24648,7 @@
         <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>20</v>
@@ -24838,22 +24657,22 @@
         <v>20</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>592</v>
+        <v>283</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>593</v>
+        <v>284</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>497</v>
+        <v>285</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>498</v>
+        <v>286</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>20</v>
@@ -24902,19 +24721,19 @@
         <v>20</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>591</v>
+        <v>287</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>20</v>
@@ -24926,10 +24745,10 @@
         <v>20</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>500</v>
+        <v>288</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>501</v>
+        <v>289</v>
       </c>
       <c r="AP178" t="s" s="2">
         <v>20</v>
@@ -24938,16 +24757,14 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>745</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>20</v>
       </c>
@@ -24959,7 +24776,7 @@
         <v>93</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>20</v>
@@ -24968,19 +24785,19 @@
         <v>94</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>494</v>
+        <v>247</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>746</v>
+        <v>582</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>566</v>
+        <v>355</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>747</v>
+        <v>583</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>568</v>
+        <v>357</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>20</v>
@@ -25005,13 +24822,11 @@
         <v>20</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y179" s="2"/>
       <c r="Z179" t="s" s="2">
-        <v>20</v>
+        <v>743</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>20</v>
@@ -25029,13 +24844,13 @@
         <v>20</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>105</v>
@@ -25050,27 +24865,27 @@
         <v>20</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>20</v>
+        <v>584</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>571</v>
+        <v>360</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>572</v>
+        <v>361</v>
       </c>
       <c r="AP179" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ179" t="s" s="2">
-        <v>20</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25093,16 +24908,20 @@
         <v>20</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>110</v>
+        <v>586</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O180" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P180" t="s" s="2">
         <v>20</v>
       </c>
@@ -25126,13 +24945,13 @@
         <v>20</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>20</v>
@@ -25150,7 +24969,7 @@
         <v>20</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>112</v>
+        <v>585</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -25159,10 +24978,10 @@
         <v>93</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>20</v>
+        <v>434</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>20</v>
@@ -25174,10 +24993,10 @@
         <v>20</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>113</v>
+        <v>435</v>
       </c>
       <c r="AP180" t="s" s="2">
         <v>20</v>
@@ -25188,14 +25007,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>115</v>
+        <v>437</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -25214,18 +25033,20 @@
         <v>20</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>116</v>
+        <v>247</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>117</v>
+        <v>438</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>118</v>
+        <v>439</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O181" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>20</v>
       </c>
@@ -25249,31 +25070,31 @@
         <v>20</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>123</v>
+        <v>589</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -25285,7 +25106,7 @@
         <v>105</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>20</v>
@@ -25294,31 +25115,31 @@
         <v>20</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>20</v>
+        <v>444</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="AO181" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="AP181" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ181" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>505</v>
+        <v>20</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
@@ -25331,25 +25152,25 @@
         <v>20</v>
       </c>
       <c r="I182" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>506</v>
+        <v>591</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>507</v>
+        <v>592</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>119</v>
+        <v>496</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>202</v>
+        <v>497</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>20</v>
@@ -25398,7 +25219,7 @@
         <v>20</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>508</v>
+        <v>590</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -25407,10 +25228,10 @@
         <v>82</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>20</v>
@@ -25422,4004 +25243,20 @@
         <v>20</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>107</v>
+        <v>500</v>
       </c>
       <c r="AP182" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AQ182" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="183" hidden="true">
-      <c r="A183" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AN183" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO183" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP183" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AQ183" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y184" s="2"/>
-      <c r="Z184" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM184" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN184" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO184" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AP184" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ184" t="s" s="2">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN185" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO185" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AP185" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ185" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="186" hidden="true">
-      <c r="A186" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM186" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN186" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AO186" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AP186" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ186" t="s" s="2">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="187" hidden="true">
-      <c r="A187" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ187" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="D188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E188" s="2"/>
-      <c r="F188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G188" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H188" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J188" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K188" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="L188" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="M188" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q188" s="2"/>
-      <c r="R188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF188" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG188" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI188" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ188" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN188" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AO188" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AP188" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ188" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="189" hidden="true">
-      <c r="A189" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G189" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K189" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L189" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
-      <c r="P189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q189" s="2"/>
-      <c r="R189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF189" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG189" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH189" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO189" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AP189" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ189" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="190" hidden="true">
-      <c r="A190" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K190" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M190" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N190" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q190" s="2"/>
-      <c r="R190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB190" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE190" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF190" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG190" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH190" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI190" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ190" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO190" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP190" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ190" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="191" hidden="true">
-      <c r="A191" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J191" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K191" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L191" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M191" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="P191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q191" s="2"/>
-      <c r="R191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF191" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG191" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH191" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI191" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO191" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP191" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ191" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="192" hidden="true">
-      <c r="A192" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G192" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J192" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K192" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L192" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M192" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O192" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q192" s="2"/>
-      <c r="R192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S192" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="T192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X192" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y192" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Z192" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AA192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF192" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG192" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH192" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI192" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ192" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL192" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM192" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AN192" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO192" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP192" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AQ192" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="193" hidden="true">
-      <c r="A193" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C193" s="2"/>
-      <c r="D193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G193" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J193" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K193" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L193" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q193" s="2"/>
-      <c r="R193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X193" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="Y193" s="2"/>
-      <c r="Z193" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="AA193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF193" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG193" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH193" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI193" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ193" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM193" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN193" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO193" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AP193" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ193" t="s" s="2">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="194" hidden="true">
-      <c r="A194" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C194" s="2"/>
-      <c r="D194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G194" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K194" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q194" s="2"/>
-      <c r="R194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X194" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y194" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="Z194" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AA194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF194" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH194" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI194" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AJ194" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AP194" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ194" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="195" hidden="true">
-      <c r="A195" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K195" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L195" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O195" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q195" s="2"/>
-      <c r="R195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X195" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y195" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="Z195" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF195" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG195" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH195" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI195" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ195" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM195" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN195" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AO195" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AP195" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ195" t="s" s="2">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="196" hidden="true">
-      <c r="A196" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K196" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L196" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q196" s="2"/>
-      <c r="R196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF196" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG196" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH196" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN196" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO196" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP196" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ196" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="D197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G197" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H197" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J197" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K197" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="L197" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q197" s="2"/>
-      <c r="R197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF197" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG197" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI197" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ197" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN197" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AO197" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AP197" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ197" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="198" hidden="true">
-      <c r="A198" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C198" s="2"/>
-      <c r="D198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G198" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K198" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L198" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M198" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" s="2"/>
-      <c r="P198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q198" s="2"/>
-      <c r="R198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF198" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG198" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH198" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO198" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AP198" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ198" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="199" hidden="true">
-      <c r="A199" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K199" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L199" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M199" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O199" s="2"/>
-      <c r="P199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q199" s="2"/>
-      <c r="R199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB199" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AC199" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE199" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF199" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG199" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH199" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI199" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ199" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO199" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP199" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ199" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="200" hidden="true">
-      <c r="A200" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I200" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J200" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K200" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="P200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q200" s="2"/>
-      <c r="R200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF200" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG200" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH200" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI200" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ200" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO200" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP200" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ200" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="201" hidden="true">
-      <c r="A201" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C201" s="2"/>
-      <c r="D201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G201" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K201" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L201" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M201" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q201" s="2"/>
-      <c r="R201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S201" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="T201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X201" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y201" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Z201" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AA201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF201" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG201" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH201" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI201" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ201" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL201" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM201" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AN201" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO201" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP201" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AQ201" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="202" hidden="true">
-      <c r="A202" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C202" s="2"/>
-      <c r="D202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E202" s="2"/>
-      <c r="F202" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G202" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J202" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K202" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L202" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q202" s="2"/>
-      <c r="R202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF202" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG202" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH202" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI202" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ202" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM202" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN202" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO202" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AP202" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ202" t="s" s="2">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="203" hidden="true">
-      <c r="A203" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C203" s="2"/>
-      <c r="D203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E203" s="2"/>
-      <c r="F203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G203" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K203" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L203" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q203" s="2"/>
-      <c r="R203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X203" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y203" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="Z203" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AA203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF203" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG203" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH203" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI203" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AJ203" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN203" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO203" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AP203" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ203" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="204" hidden="true">
-      <c r="A204" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C204" s="2"/>
-      <c r="D204" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="E204" s="2"/>
-      <c r="F204" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K204" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L204" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q204" s="2"/>
-      <c r="R204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X204" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y204" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="Z204" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF204" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG204" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH204" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI204" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ204" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM204" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN204" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AO204" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AP204" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ204" t="s" s="2">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="205" hidden="true">
-      <c r="A205" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C205" s="2"/>
-      <c r="D205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E205" s="2"/>
-      <c r="F205" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K205" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L205" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q205" s="2"/>
-      <c r="R205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF205" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG205" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH205" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN205" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO205" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP205" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ205" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C206" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="D206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E206" s="2"/>
-      <c r="F206" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G206" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H206" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J206" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K206" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="L206" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="M206" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="P206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q206" s="2"/>
-      <c r="R206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF206" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG206" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH206" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI206" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ206" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN206" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AO206" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AP206" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ206" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="207" hidden="true">
-      <c r="A207" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C207" s="2"/>
-      <c r="D207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E207" s="2"/>
-      <c r="F207" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G207" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K207" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L207" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M207" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
-      <c r="P207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q207" s="2"/>
-      <c r="R207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF207" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG207" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH207" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO207" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AP207" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ207" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="208" hidden="true">
-      <c r="A208" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C208" s="2"/>
-      <c r="D208" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="E208" s="2"/>
-      <c r="F208" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G208" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K208" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L208" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M208" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O208" s="2"/>
-      <c r="P208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q208" s="2"/>
-      <c r="R208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB208" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AC208" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AD208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE208" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF208" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG208" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH208" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI208" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ208" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO208" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP208" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ208" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="209" hidden="true">
-      <c r="A209" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C209" s="2"/>
-      <c r="D209" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="E209" s="2"/>
-      <c r="F209" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G209" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I209" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J209" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K209" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="L209" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="P209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q209" s="2"/>
-      <c r="R209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF209" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG209" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH209" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI209" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ209" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO209" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AP209" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ209" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="210" hidden="true">
-      <c r="A210" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="C210" s="2"/>
-      <c r="D210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E210" s="2"/>
-      <c r="F210" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G210" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J210" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K210" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L210" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M210" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="P210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q210" s="2"/>
-      <c r="R210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S210" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="T210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X210" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y210" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="Z210" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AA210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF210" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AG210" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH210" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI210" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ210" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL210" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM210" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AN210" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO210" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AP210" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AQ210" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="211" hidden="true">
-      <c r="A211" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C211" s="2"/>
-      <c r="D211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E211" s="2"/>
-      <c r="F211" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G211" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J211" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K211" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="L211" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M211" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O211" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q211" s="2"/>
-      <c r="R211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF211" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG211" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH211" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI211" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ211" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM211" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AN211" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO211" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AP211" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ211" t="s" s="2">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="212" hidden="true">
-      <c r="A212" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C212" s="2"/>
-      <c r="D212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E212" s="2"/>
-      <c r="F212" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G212" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K212" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L212" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="M212" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="P212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q212" s="2"/>
-      <c r="R212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X212" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y212" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="Z212" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AA212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF212" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AG212" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH212" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI212" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AJ212" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN212" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO212" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AP212" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ212" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="213" hidden="true">
-      <c r="A213" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="C213" s="2"/>
-      <c r="D213" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="E213" s="2"/>
-      <c r="F213" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G213" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K213" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L213" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="M213" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="P213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q213" s="2"/>
-      <c r="R213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X213" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y213" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="Z213" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF213" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG213" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH213" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI213" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AJ213" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM213" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN213" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AO213" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AP213" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ213" t="s" s="2">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="214" hidden="true">
-      <c r="A214" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="B214" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C214" s="2"/>
-      <c r="D214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E214" s="2"/>
-      <c r="F214" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G214" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K214" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L214" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M214" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="P214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q214" s="2"/>
-      <c r="R214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF214" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG214" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH214" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN214" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO214" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP214" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AQ214" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ214">
+  <autoFilter ref="A1:AQ182">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -29429,7 +25266,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI213">
+  <conditionalFormatting sqref="A2:AI181">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-follow-up.xlsx
+++ b/ci-build/StructureDefinition-senologie-follow-up.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
